--- a/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,82; 25,9</t>
+          <t>9,94; 26,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 19,84</t>
+          <t>2,23; 19,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 26,35</t>
+          <t>8,44; 25,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,83; 34,33</t>
+          <t>19,2; 35,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 22,53</t>
+          <t>6,39; 24,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,66; 25,6</t>
+          <t>11,0; 26,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,22; 29,09</t>
+          <t>16,6; 28,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 19,87</t>
+          <t>7,32; 19,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,51; 24,86</t>
+          <t>11,28; 23,4</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,31; 69,28</t>
+          <t>21,3; 70,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 52,3</t>
+          <t>4,55; 51,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,9; 70,5</t>
+          <t>18,94; 69,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,34; 77,09</t>
+          <t>35,71; 81,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,56; 50,53</t>
+          <t>11,6; 54,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,55; 57,31</t>
+          <t>20,23; 60,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,98; 68,53</t>
+          <t>34,19; 67,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,79; 47,43</t>
+          <t>14,8; 45,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,95; 59,8</t>
+          <t>22,31; 54,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 16,8</t>
+          <t>4,26; 17,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,16; 21,85</t>
+          <t>9,18; 21,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,3; -0,45</t>
+          <t>-14,56; -0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 14,56</t>
+          <t>2,1; 14,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,92</t>
+          <t>3,45; 15,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,45; -16,35</t>
+          <t>-28,05; -16,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,92</t>
+          <t>4,99; 14,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 17,03</t>
+          <t>8,24; 16,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -10,59</t>
+          <t>-19,38; -9,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 45,09</t>
+          <t>9,7; 47,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,13; 58,83</t>
+          <t>21,1; 59,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,39; -1,21</t>
+          <t>-34,2; -2,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 25,47</t>
+          <t>3,4; 25,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 28,59</t>
+          <t>5,27; 26,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-43,53; -28,09</t>
+          <t>-44,86; -29,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,63; 29,21</t>
+          <t>9,56; 29,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 35,45</t>
+          <t>15,89; 35,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,3; -21,84</t>
+          <t>-37,34; -20,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,89; 22,53</t>
+          <t>7,45; 22,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,88</t>
+          <t>-0,07; 15,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,26; 4,6</t>
+          <t>-10,4; 4,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 7,14</t>
+          <t>-7,9; 7,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,39; 0,07</t>
+          <t>-14,19; -0,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,05; -15,57</t>
+          <t>-29,3; -15,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,57</t>
+          <t>1,74; 12,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 6,31</t>
+          <t>-5,26; 5,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,2; -7,87</t>
+          <t>-18,46; -8,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,67; 57,19</t>
+          <t>15,52; 56,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 36,55</t>
+          <t>-0,25; 39,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 11,24</t>
+          <t>-22,13; 11,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 11,04</t>
+          <t>-11,15; 11,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 0,07</t>
+          <t>-19,82; -0,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,38; -24,22</t>
+          <t>-41,24; -23,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 23,39</t>
+          <t>3,01; 23,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 11,76</t>
+          <t>-8,99; 10,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -14,7</t>
+          <t>-31,71; -15,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 13,96</t>
+          <t>-0,84; 13,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 12,45</t>
+          <t>-2,11; 12,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,55; -0,25</t>
+          <t>-18,02; -1,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 7,62</t>
+          <t>-5,35; 8,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 7,27</t>
+          <t>-5,29; 7,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,54; -19,17</t>
+          <t>-44,57; -19,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 8,75</t>
+          <t>-1,45; 8,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 8,28</t>
+          <t>-1,92; 8,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-30,67; -13,0</t>
+          <t>-31,13; -12,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 29,66</t>
+          <t>-1,22; 29,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 27,55</t>
+          <t>-4,08; 25,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,58; -0,94</t>
+          <t>-33,47; -2,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 11,78</t>
+          <t>-7,41; 12,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 11,1</t>
+          <t>-7,55; 11,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,93; -28,2</t>
+          <t>-65,85; -28,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 15,38</t>
+          <t>-2,32; 15,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 14,41</t>
+          <t>-3,17; 14,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-50,4; -22,36</t>
+          <t>-51,22; -22,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 20,25</t>
+          <t>0,38; 19,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 18,01</t>
+          <t>-2,03; 16,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-40,61; -25,38</t>
+          <t>-41,83; -26,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,89; 30,63</t>
+          <t>13,44; 31,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 12,57</t>
+          <t>-6,38; 12,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-55,76; -39,53</t>
+          <t>-55,29; -39,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,71; 23,17</t>
+          <t>9,53; 23,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 12,37</t>
+          <t>-1,47; 12,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-46,64; -35,25</t>
+          <t>-46,94; -35,76</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,76; 51,4</t>
+          <t>0,61; 49,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 46,37</t>
+          <t>-4,17; 43,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,25; -65,82</t>
+          <t>-84,91; -66,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,54; 59,76</t>
+          <t>21,32; 60,7</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 24,84</t>
+          <t>-10,18; 24,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-90,78; -76,69</t>
+          <t>-91,22; -77,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,1; 49,7</t>
+          <t>17,64; 50,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 26,41</t>
+          <t>-2,84; 25,65</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-86,82; -75,17</t>
+          <t>-86,99; -75,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,36; 21,34</t>
+          <t>3,62; 20,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 3,53</t>
+          <t>-14,65; 3,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 7,15</t>
+          <t>-8,76; 7,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,5; 20,71</t>
+          <t>5,67; 21,03</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 0,61</t>
+          <t>-14,85; 1,61</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,76; -5,44</t>
+          <t>-20,69; -5,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,24; 18,6</t>
+          <t>7,38; 18,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,32; -0,28</t>
+          <t>-12,25; -0,98</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,42; -1,24</t>
+          <t>-12,01; -1,46</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7,78; 47,2</t>
+          <t>6,85; 44,7</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,63; 8,12</t>
+          <t>-26,56; 7,67</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 15,33</t>
+          <t>-16,25; 16,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,83; 34,75</t>
+          <t>8,22; 35,96</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 0,98</t>
+          <t>-22,35; 2,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-31,3; -9,29</t>
+          <t>-30,14; -8,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,4; 34,13</t>
+          <t>12,27; 34,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -0,61</t>
+          <t>-20,8; -1,92</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-20,61; -2,21</t>
+          <t>-20,2; -2,89</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10,66; 21,92</t>
+          <t>10,61; 21,91</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 7,39</t>
+          <t>-4,93; 6,65</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,49; -13,4</t>
+          <t>-24,26; -13,73</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,43; 14,49</t>
+          <t>4,1; 14,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 1,34</t>
+          <t>-9,71; 1,33</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-33,12; 13,21</t>
+          <t>-33,16; 13,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,89; 16,53</t>
+          <t>8,68; 16,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,85</t>
+          <t>-5,44; 2,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 11,26</t>
+          <t>-26,48; 8,86</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,45; 56,79</t>
+          <t>24,29; 57,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 19,54</t>
+          <t>-11,35; 17,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,09; -34,13</t>
+          <t>-55,34; -33,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5,64; 26,21</t>
+          <t>6,55; 26,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 2,23</t>
+          <t>-15,92; 2,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,94; 24,56</t>
+          <t>-56,23; 22,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,03; 34,3</t>
+          <t>16,72; 35,1</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 5,92</t>
+          <t>-10,37; 5,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 23,05</t>
+          <t>-52,73; 17,77</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 3,09</t>
+          <t>-7,64; 2,43</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 7,44</t>
+          <t>-3,02; 7,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-38,0; -14,62</t>
+          <t>-37,15; -14,26</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 2,95</t>
+          <t>-7,15; 2,88</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 5,3</t>
+          <t>-4,29; 5,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-21,71; -12,28</t>
+          <t>-21,6; -12,15</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,59</t>
+          <t>-5,82; 1,76</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 4,73</t>
+          <t>-2,12; 4,9</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-33,19; -15,28</t>
+          <t>-34,79; -15,53</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 6,67</t>
+          <t>-15,87; 5,65</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 17,18</t>
+          <t>-6,1; 15,83</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-79,36; -32,63</t>
+          <t>-78,83; -31,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 5,16</t>
+          <t>-11,73; 5,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 9,41</t>
+          <t>-7,17; 9,46</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-35,99; -22,07</t>
+          <t>-35,62; -21,81</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 3,2</t>
+          <t>-10,76; 3,41</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 9,38</t>
+          <t>-3,95; 9,75</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-64,13; -29,52</t>
+          <t>-65,38; -30,24</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>7,08; 12,12</t>
+          <t>7,03; 11,76</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,95</t>
+          <t>2,75; 7,73</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -8,91</t>
+          <t>-20,14; -8,9</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,46</t>
+          <t>4,95; 9,7</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,08</t>
+          <t>-1,39; 3,13</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -7,55</t>
+          <t>-22,68; -7,17</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,07</t>
+          <t>6,68; 10,07</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,94</t>
+          <t>1,43; 4,7</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-18,82; -9,31</t>
+          <t>-18,83; -9,65</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>15,39; 28,18</t>
+          <t>15,37; 27,37</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>6,06; 18,5</t>
+          <t>5,99; 17,99</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-42,66; -20,33</t>
+          <t>-44,75; -20,32</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,05</t>
+          <t>8,05; 16,51</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 5,24</t>
+          <t>-2,23; 5,28</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-37,11; -12,58</t>
+          <t>-37,36; -11,81</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,53; 19,61</t>
+          <t>12,4; 19,49</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,62</t>
+          <t>2,72; 9,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-35,85; -17,9</t>
+          <t>-35,72; -18,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>13,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,23</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,78</t>
+          <t>14,2</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 26,13</t>
+          <t>9,91; 26,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 19,68</t>
+          <t>2,36; 20,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,44; 25,58</t>
+          <t>5,22; 21,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,2; 35,9</t>
+          <t>18,91; 35,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 24,03</t>
+          <t>6,56; 23,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 26,54</t>
+          <t>6,33; 21,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,6; 28,58</t>
+          <t>16,7; 28,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 19,17</t>
+          <t>7,22; 19,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,28; 23,4</t>
+          <t>8,54; 20,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,3; 70,45</t>
+          <t>21,01; 70,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 51,7</t>
+          <t>5,62; 55,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 69,29</t>
+          <t>11,19; 58,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,71; 81,94</t>
+          <t>34,64; 77,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 54,58</t>
+          <t>11,72; 52,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,23; 60,7</t>
+          <t>10,03; 49,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,19; 67,46</t>
+          <t>34,02; 66,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,8; 45,17</t>
+          <t>14,59; 44,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,31; 54,86</t>
+          <t>17,36; 47,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,47</t>
+          <t>-7,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-22,13</t>
+          <t>-22,84</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-14,92</t>
+          <t>-15,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,12</t>
+          <t>4,05; 16,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,18; 21,66</t>
+          <t>9,26; 21,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,56; -0,86</t>
+          <t>-14,92; -1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 14,32</t>
+          <t>2,49; 14,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 15,49</t>
+          <t>3,91; 15,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,05; -16,72</t>
+          <t>-28,52; -16,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 14,08</t>
+          <t>5,06; 13,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,24; 16,9</t>
+          <t>8,24; 16,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -9,74</t>
+          <t>-20,0; -10,74</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,53%</t>
+          <t>-19,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-36,84%</t>
+          <t>-38,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-29,65%</t>
+          <t>-30,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 47,06</t>
+          <t>9,16; 44,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,1; 59,18</t>
+          <t>21,15; 59,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,2; -2,55</t>
+          <t>-33,71; -4,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 25,15</t>
+          <t>3,95; 24,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,27; 26,94</t>
+          <t>6,2; 27,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,86; -29,18</t>
+          <t>-45,18; -29,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 29,32</t>
+          <t>9,58; 28,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,89; 35,57</t>
+          <t>15,48; 36,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-37,34; -20,85</t>
+          <t>-38,0; -22,47</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-3,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-22,38</t>
+          <t>-22,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-12,9</t>
+          <t>-13,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,45; 22,93</t>
+          <t>7,92; 22,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 15,52</t>
+          <t>-0,68; 14,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 4,55</t>
+          <t>-10,99; 3,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 7,22</t>
+          <t>-7,9; 6,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -0,18</t>
+          <t>-13,64; 1,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,3; -15,17</t>
+          <t>-29,23; -15,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 12,51</t>
+          <t>2,07; 13,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,32</t>
+          <t>-5,22; 5,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,46; -8,16</t>
+          <t>-18,54; -8,4</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-6,94%</t>
+          <t>-8,49%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-33,16%</t>
+          <t>-33,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-23,07%</t>
+          <t>-23,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,52; 56,4</t>
+          <t>16,86; 59,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 39,05</t>
+          <t>-1,47; 37,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,13; 11,05</t>
+          <t>-23,82; 9,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 11,46</t>
+          <t>-11,12; 10,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,82; -0,23</t>
+          <t>-19,15; 1,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,24; -23,87</t>
+          <t>-41,41; -24,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 23,54</t>
+          <t>3,46; 24,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 10,08</t>
+          <t>-8,81; 10,87</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,71; -15,2</t>
+          <t>-31,29; -15,71</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-9,47</t>
+          <t>-10,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-30,19</t>
+          <t>-19,99</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-20,23</t>
+          <t>-14,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 13,58</t>
+          <t>-0,85; 13,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 12,08</t>
+          <t>-3,06; 12,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,02; -1,41</t>
+          <t>-18,72; -1,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 8,06</t>
+          <t>-5,24; 7,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 7,47</t>
+          <t>-5,45; 7,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,57; -19,05</t>
+          <t>-26,51; -13,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 8,63</t>
+          <t>-1,04; 9,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 8,41</t>
+          <t>-1,56; 8,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-31,13; -12,87</t>
+          <t>-19,82; -9,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-18,79%</t>
+          <t>-20,03%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-43,86%</t>
+          <t>-29,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-33,84%</t>
+          <t>-25,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 29,99</t>
+          <t>-1,53; 29,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 25,58</t>
+          <t>-5,47; 26,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,47; -2,84</t>
+          <t>-34,82; -4,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 12,27</t>
+          <t>-7,32; 12,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 11,73</t>
+          <t>-7,47; 10,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,85; -28,19</t>
+          <t>-37,05; -20,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 15,05</t>
+          <t>-1,67; 15,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 14,83</t>
+          <t>-2,55; 15,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,22; -22,25</t>
+          <t>-32,41; -16,77</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-33,53</t>
+          <t>-34,3</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-47,77</t>
+          <t>-45,7</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-40,77</t>
+          <t>-40,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 19,45</t>
+          <t>0,27; 19,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 16,78</t>
+          <t>-1,62; 18,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-41,83; -26,3</t>
+          <t>-42,72; -26,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,44; 31,38</t>
+          <t>13,64; 31,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 12,95</t>
+          <t>-5,95; 12,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -39,59</t>
+          <t>-53,39; -38,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,53; 23,48</t>
+          <t>8,9; 22,95</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 12,25</t>
+          <t>-1,65; 12,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-46,94; -35,76</t>
+          <t>-45,69; -34,46</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-76,89%</t>
+          <t>-78,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-83,29%</t>
+          <t>-79,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-80,65%</t>
+          <t>-79,15%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,61; 49,82</t>
+          <t>0,56; 50,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 43,61</t>
+          <t>-3,22; 46,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,91; -66,42</t>
+          <t>-85,32; -68,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21,32; 60,7</t>
+          <t>22,63; 59,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 24,94</t>
+          <t>-9,33; 23,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-91,22; -77,17</t>
+          <t>-84,69; -73,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,64; 50,63</t>
+          <t>16,51; 50,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 25,65</t>
+          <t>-3,18; 26,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-86,99; -75,46</t>
+          <t>-83,57; -74,13</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-13,02</t>
+          <t>-13,61</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,96</t>
+          <t>-7,28</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,62; 20,26</t>
+          <t>3,85; 20,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 3,48</t>
+          <t>-13,9; 3,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 7,88</t>
+          <t>-8,71; 7,46</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,67; 21,03</t>
+          <t>4,59; 20,9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 1,61</t>
+          <t>-16,54; 0,89</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -5,21</t>
+          <t>-20,78; -5,88</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,38; 18,44</t>
+          <t>7,19; 18,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -0,98</t>
+          <t>-12,14; -0,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,01; -1,46</t>
+          <t>-13,45; -1,93</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-1,36%</t>
+          <t>-1,52%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-20,41%</t>
+          <t>-21,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-12,2%</t>
+          <t>-12,76%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,85; 44,7</t>
+          <t>6,91; 44,36</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 7,67</t>
+          <t>-25,66; 6,81</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 16,94</t>
+          <t>-15,81; 16,73</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8,22; 35,96</t>
+          <t>6,82; 35,76</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 2,61</t>
+          <t>-24,31; 1,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-30,14; -8,74</t>
+          <t>-31,31; -10,26</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,27; 34,24</t>
+          <t>12,07; 34,59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,8; -1,92</t>
+          <t>-20,25; -0,41</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-20,2; -2,89</t>
+          <t>-22,36; -3,48</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-19,11</t>
+          <t>-19,92</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-13,79</t>
+          <t>-30,96</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-14,89</t>
+          <t>-25,49</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>10,61; 21,91</t>
+          <t>11,01; 22,44</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,65</t>
+          <t>-4,12; 7,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-24,26; -13,73</t>
+          <t>-25,28; -14,5</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,48</t>
+          <t>3,87; 14,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 1,33</t>
+          <t>-10,24; 0,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-33,16; 13,12</t>
+          <t>-36,22; -26,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,68; 16,71</t>
+          <t>8,68; 16,53</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,46</t>
+          <t>-5,33; 2,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 8,86</t>
+          <t>-29,26; -21,99</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-46,48%</t>
+          <t>-48,45%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-23,63%</t>
+          <t>-53,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-29,84%</t>
+          <t>-51,09%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>24,29; 57,18</t>
+          <t>24,68; 58,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 17,48</t>
+          <t>-9,39; 18,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,34; -33,91</t>
+          <t>-57,65; -37,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,55; 26,18</t>
+          <t>6,26; 26,52</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 2,35</t>
+          <t>-16,56; 1,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-56,23; 22,99</t>
+          <t>-58,78; -46,92</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,72; 35,1</t>
+          <t>16,51; 34,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 5,08</t>
+          <t>-10,39; 5,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 17,77</t>
+          <t>-56,25; -45,47</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-24,13</t>
+          <t>-17,26</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-16,92</t>
+          <t>-17,36</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-21,93</t>
+          <t>-17,34</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,43</t>
+          <t>-8,44; 2,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 7,0</t>
+          <t>-3,34; 7,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-37,15; -14,26</t>
+          <t>-22,49; -12,54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 2,88</t>
+          <t>-6,7; 3,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,31</t>
+          <t>-4,62; 5,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -12,15</t>
+          <t>-21,87; -12,62</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 1,76</t>
+          <t>-6,3; 1,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 4,9</t>
+          <t>-2,43; 4,78</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-34,79; -15,53</t>
+          <t>-20,82; -13,86</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-52,31%</t>
+          <t>-37,41%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-29,01%</t>
+          <t>-29,75%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-41,86%</t>
+          <t>-33,1%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 5,65</t>
+          <t>-17,25; 5,6</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 15,83</t>
+          <t>-6,74; 17,19</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-78,83; -31,96</t>
+          <t>-45,55; -28,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 5,05</t>
+          <t>-11,0; 6,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 9,46</t>
+          <t>-7,71; 9,86</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-35,62; -21,81</t>
+          <t>-35,92; -22,51</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 3,41</t>
+          <t>-11,48; 2,75</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 9,75</t>
+          <t>-4,56; 9,59</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-65,38; -30,24</t>
+          <t>-38,3; -27,06</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-12,44</t>
+          <t>-11,48</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-18,24</t>
+          <t>-20,69</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-15,28</t>
+          <t>-16,11</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,76</t>
+          <t>6,9; 11,92</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,73</t>
+          <t>2,69; 7,78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -8,9</t>
+          <t>-14,1; -9,22</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,7</t>
+          <t>4,84; 9,48</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,13</t>
+          <t>-1,51; 3,33</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-22,68; -7,17</t>
+          <t>-22,65; -18,71</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,07</t>
+          <t>6,67; 10,08</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,7</t>
+          <t>1,39; 4,82</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-18,83; -9,65</t>
+          <t>-17,8; -14,42</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-28,04%</t>
+          <t>-25,87%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-30,2%</t>
+          <t>-34,27%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-29,11%</t>
+          <t>-30,69%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>15,37; 27,37</t>
+          <t>15,06; 27,68</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5,99; 17,99</t>
+          <t>5,84; 18,0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-44,75; -20,32</t>
+          <t>-30,82; -21,25</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>8,05; 16,51</t>
+          <t>7,81; 16,09</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 5,28</t>
+          <t>-2,47; 5,6</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-37,36; -11,81</t>
+          <t>-36,92; -31,5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,4; 19,49</t>
+          <t>12,43; 19,6</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,18</t>
+          <t>2,59; 9,35</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -18,52</t>
+          <t>-33,44; -27,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
